--- a/duoki_editor/resources/data/save/TemplateConfig_save.xlsx
+++ b/duoki_editor/resources/data/save/TemplateConfig_save.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\projects\DuokiEditor\duoki_editor\resources\data\save\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A228201-57AD-4AD0-9F52-E9E4EF191F41}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E738EA7-0061-4B5A-A07A-747CC0B43F40}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="9555" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="46">
   <si>
     <t>id</t>
   </si>
@@ -163,33 +163,6 @@
   </si>
   <si>
     <t>商店-剧情-1</t>
-  </si>
-  <si>
-    <t>商店_限时找实体道具_0_1_通用_a5_e0</t>
-  </si>
-  <si>
-    <t>商店-限时找实体道具-1</t>
-  </si>
-  <si>
-    <t>限时找实体道具</t>
-  </si>
-  <si>
-    <t>商店_限时找地图道具_0_1_通用_a5_e0</t>
-  </si>
-  <si>
-    <t>商店-限时找地图道具-1</t>
-  </si>
-  <si>
-    <t>限时找地图道具</t>
-  </si>
-  <si>
-    <t>商店_限时找混合道具_0_1_通用_a5_e0</t>
-  </si>
-  <si>
-    <t>商店-限时找混合道具-1</t>
-  </si>
-  <si>
-    <t>限时找混合道具</t>
   </si>
 </sst>
 </file>
@@ -1161,7 +1134,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{971344F8-DA97-4A3F-BA3F-9BE0B32D3805}">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.15">
@@ -1254,102 +1227,6 @@
         <v>10</v>
       </c>
       <c r="J3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>10</v>
-      </c>
-      <c r="J4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" t="s">
-        <v>50</v>
-      </c>
-      <c r="E5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F5" t="s">
-        <v>50</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>10</v>
-      </c>
-      <c r="J5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" t="s">
-        <v>53</v>
-      </c>
-      <c r="E6" t="s">
-        <v>54</v>
-      </c>
-      <c r="F6" t="s">
-        <v>53</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>10</v>
-      </c>
-      <c r="J6" t="s">
         <v>28</v>
       </c>
     </row>
